--- a/plantillas/Plantilla_Base_Grupo.xlsx
+++ b/plantillas/Plantilla_Base_Grupo.xlsx
@@ -1964,7 +1964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1972,7 +1972,8 @@
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2017,6 +2018,11 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
           <t>mostrar_en_web</t>
         </is>
       </c>
@@ -2045,7 +2051,8 @@
           <t>Qué pasó ese año.</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr"/>
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2072,10 +2079,11 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Qué pasó.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+          <t>Qué pasó. El link es opcional: si está, el hito muestra un botón «Visitar ↗».</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2087,7 +2095,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F4:F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escribí TRUE o FALSE." promptTitle="TRUE o FALSE" prompt="TRUE = sí · FALSE = no · vacío = TRUE" type="list">
+    <dataValidation sqref="G4:G60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escribí TRUE o FALSE." promptTitle="TRUE o FALSE" prompt="TRUE = sí · FALSE = no · vacío = TRUE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
